--- a/examples/excel/charts/charts-area.xlsx
+++ b/examples/excel/charts/charts-area.xlsx
@@ -3,11 +3,11 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Area Fundamentals" sheetId="2" r:id="Re46bab51e9784ddd"/>
-    <x:sheet name="2-Area Variants" sheetId="3" r:id="R2d2b3fc0419748cc"/>
-    <x:sheet name="3-Area Styling" sheetId="4" r:id="R130ee8a7d76d4b0f"/>
-    <x:sheet name="4-Labels &amp; Legend" sheetId="5" r:id="Raa12c09eee24437c"/>
-    <x:sheet name="5-Advanced" sheetId="6" r:id="Ra2a33cef849843e5"/>
+    <x:sheet name="1-Area Fundamentals" sheetId="2" r:id="R6137bfa563194d5d"/>
+    <x:sheet name="2-Area Variants" sheetId="3" r:id="R18c6c63060e34ebc"/>
+    <x:sheet name="3-Area Styling" sheetId="4" r:id="Ree3e1459b93b4b5c"/>
+    <x:sheet name="4-Labels &amp; Legend" sheetId="5" r:id="Ra379de6191d44b8b"/>
+    <x:sheet name="5-Advanced" sheetId="6" r:id="R14267afd6af744ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1507,6 +1507,29 @@
               </a:srgbClr>
             </a:solidFill>
           </c:spPr>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="6"/>
@@ -1819,6 +1842,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:overlay val="1"/>
       <c:txPr>
         <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
@@ -1834,7 +1858,6 @@
           </a:pPr>
         </a:p>
       </c:txPr>
-      <c:overlay val="1"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -2215,7 +2238,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -4573,6 +4596,7 @@
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:area3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -4606,6 +4630,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -4827,6 +4860,7 @@
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:area3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -4869,6 +4903,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -5052,7 +5095,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R945b69595fc549e9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f55702631aa4884"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5082,7 +5125,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd764d54cb64a4c67"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raeb2d0023d75457b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5112,7 +5155,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0057ae2cc0bb4662"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2afb32d3aa5a44ff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5142,7 +5185,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R62c83e015d93473e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a548db0036f44cc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5177,7 +5220,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b516f19cdba4cf6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R46285adea04940fe"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5207,7 +5250,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcf9eafbbb06f40b2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6be121578c14465"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5237,7 +5280,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31a71fa12f37409a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R353eb559467145aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5267,7 +5310,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R33fc057b8cc94cbc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R11698fe43c9341af"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5302,7 +5345,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf84c4b2fb8774ee1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R13e67d7262aa46c9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5332,7 +5375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2dec746f0f14370"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R70f358cac9e64926"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5362,7 +5405,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R93f86d69eff4443e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcfb72fe983894a4b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5392,7 +5435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1bf95488a0942f2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6d8a2f03adb34a22"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5427,7 +5470,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad18ed75a6824ecb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f604715fa3d4ff8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5457,7 +5500,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd1a48febebe140b7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R208673f5f8934362"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5487,7 +5530,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc3aa0c43e1854bda"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14976ce485c848da"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5517,7 +5560,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc41cd7254d743e5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R60890005196f486a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5552,7 +5595,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R984bfd30bd484db9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9d1604ee2324361"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5582,7 +5625,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8baf9fe77b13436d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Racf35046bcd74925"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5612,7 +5655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbdc927570395469e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbfa4b14247a548fa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5642,7 +5685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R53ef6111f1ad4f21"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f1322c49ebe42d8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5651,6 +5694,115 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
@@ -5882,34 +6034,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab0faae49f2744c7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29d6a77927534798"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c8b718fc9e4417f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R280e6014f2594cea"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e261b50004a4ed4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R517b1a6fdede443a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3d25fa3f829478a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra210bb9c29f743f0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4f660daaf1c44a5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02836f981402418f"/>
 </x:worksheet>
 </file>